--- a/5A_Geometric.xlsx
+++ b/5A_Geometric.xlsx
@@ -461,8 +461,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,B,C,E || D |
-| b,c,d,e || a |
+          <t xml:space="preserve">| A,B,C,D,E || ∅ |
+|  b,c,d,e  || a |
 </t>
         </is>
       </c>
@@ -470,7 +470,7 @@
         <v>0.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.832449</v>
+        <v>1.873759</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -484,8 +484,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,C,D,E ||  B  |
-|   a,b   || c,d |
+          <t xml:space="preserve">| A,C,E || B,D |
+|  a,b  || c,d |
 </t>
         </is>
       </c>
@@ -493,7 +493,7 @@
         <v>0.75</v>
       </c>
       <c r="D3" t="n">
-        <v>1.787202</v>
+        <v>1.823528</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -507,8 +507,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">|  A,B,E  || C,D |
-| b,c,d,e ||  ∅  |
+          <t xml:space="preserve">| A,B,C,E || D |
+| b,c,d,e || ∅ |
 </t>
         </is>
       </c>
@@ -516,7 +516,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1.840974</v>
+        <v>1.774792</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -530,8 +530,8 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,B,E || C,D |
-| b,c,d ||  ∅  |
+          <t xml:space="preserve">| A,B,C,E || D |
+|  b,c,d  || ∅ |
 </t>
         </is>
       </c>
@@ -539,7 +539,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1.74402</v>
+        <v>1.78864</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -553,8 +553,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,B || C,D,E |
-| c,e ||   a   |
+          <t xml:space="preserve">| A,B,C,D,E || ∅ |
+|    c,e    || a |
 </t>
         </is>
       </c>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1.76879</v>
+        <v>1.83843</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -576,8 +576,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,E || B,C,D |
-| b,d ||   ∅   |
+          <t xml:space="preserve">| A,B,C,E || D |
+|   b,d   || ∅ |
 </t>
         </is>
       </c>
@@ -585,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1.793805</v>
+        <v>1.799211</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -599,16 +599,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,C,D,E ||  B  |
-|   a,b   || d,e |
+          <t xml:space="preserve">| A,C,D,E || B |
+| a,b,d,e || ∅ |
 </t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="D8" t="n">
-        <v>1.821561</v>
+        <v>1.806211</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">|  A,B,C  || D |
+          <t xml:space="preserve">| A,B,C,D || ∅ |
 | b,c,d,e || a |
 </t>
         </is>
@@ -631,7 +631,7 @@
         <v>0.5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.887446</v>
+        <v>1.89056</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -645,8 +645,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,C,D ||  B  |
-|  a,b  || c,d |
+          <t xml:space="preserve">| A,C || B,D |
+| a,b || c,d |
 </t>
         </is>
       </c>
@@ -654,7 +654,7 @@
         <v>0.75</v>
       </c>
       <c r="D10" t="n">
-        <v>1.852227</v>
+        <v>1.809347</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -668,8 +668,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">|   A,B   || C,D |
-| b,c,d,e ||  ∅  |
+          <t xml:space="preserve">|  A,B,C  || D |
+| b,c,d,e || ∅ |
 </t>
         </is>
       </c>
@@ -677,7 +677,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1.859973</v>
+        <v>1.838888</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -691,8 +691,8 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">|  A,B  || C,D |
-| b,c,d ||  ∅  |
+          <t xml:space="preserve">| A,B,C || D |
+| b,c,d || ∅ |
 </t>
         </is>
       </c>
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1.796821</v>
+        <v>1.880995</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -714,8 +714,8 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,B || C,D |
-| c,e ||  a  |
+          <t xml:space="preserve">| A,B,C,D || ∅ |
+|   c,e   || a |
 </t>
         </is>
       </c>
@@ -723,7 +723,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1.741794</v>
+        <v>1.79999</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -737,8 +737,8 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">|  A  || B,C,D |
-| b,d ||   ∅   |
+          <t xml:space="preserve">| A,B,C || D |
+|  b,d  || ∅ |
 </t>
         </is>
       </c>
@@ -746,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1.855966</v>
+        <v>1.872529</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -760,16 +760,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,C,D ||  B  |
-|  a,b  || d,e |
+          <t xml:space="preserve">|  A,C,D  || B |
+| a,b,d,e || ∅ |
 </t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="D15" t="n">
-        <v>1.933351</v>
+        <v>1.775582</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -783,8 +783,8 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">|   B   || C,D,E |
-| c,d,e ||  a,b  |
+          <t xml:space="preserve">|  B,D  || C,E |
+| c,d,e || a,b |
 </t>
         </is>
       </c>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1.879959</v>
+        <v>1.852542</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -806,8 +806,8 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">|  B  || C,D,E |
-| c,d ||  a,b  |
+          <t xml:space="preserve">| B,C,D,E || ∅ |
+| a,b,c,d || ∅ |
 </t>
         </is>
       </c>
@@ -815,7 +815,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1.902954</v>
+        <v>1.860578</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -829,8 +829,8 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">|   B,E   || C,D |
-| b,c,d,e ||  ∅  |
+          <t xml:space="preserve">|  B,C,E  || D |
+| b,c,d,e || ∅ |
 </t>
         </is>
       </c>
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.966729</v>
+        <v>1.785794</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -852,8 +852,8 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">|  B,E  || C,D |
-| b,c,d ||  ∅  |
+          <t xml:space="preserve">| B,C,E || D |
+| b,c,d || ∅ |
 </t>
         </is>
       </c>
@@ -861,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1.819069</v>
+        <v>1.768596</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -875,8 +875,8 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">|  B  || C,D,E |
-| c,e ||   a   |
+          <t xml:space="preserve">| B,C,D,E || ∅ |
+|   c,e   || a |
 </t>
         </is>
       </c>
@@ -884,7 +884,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1.783625</v>
+        <v>1.850605</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -898,8 +898,8 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">| B,C,D ||  E  |
-|   ∅   || b,d |
+          <t xml:space="preserve">| B,C,E || D |
+|  b,d  || ∅ |
 </t>
         </is>
       </c>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1.770041</v>
+        <v>1.741389</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -921,8 +921,8 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">|  B  || C,D,E |
-| d,e ||  a,b  |
+          <t xml:space="preserve">| B ||  C,D,E  |
+| ∅ || a,b,d,e |
 </t>
         </is>
       </c>
@@ -930,7 +930,7 @@
         <v>0.25</v>
       </c>
       <c r="D22" t="n">
-        <v>1.899295</v>
+        <v>1.844047</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">|   B   || C,D |
+          <t xml:space="preserve">|  B,D  ||  C  |
 | c,d,e || a,b |
 </t>
         </is>
@@ -953,7 +953,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1.860322</v>
+        <v>1.835869</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -967,8 +967,8 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">|  B  || C,D |
-| c,d || a,b |
+          <t xml:space="preserve">|  B,C,D  || ∅ |
+| a,b,c,d || ∅ |
 </t>
         </is>
       </c>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1.796082</v>
+        <v>1.764995</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -990,8 +990,8 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">|    B    || C,D |
-| b,c,d,e ||  ∅  |
+          <t xml:space="preserve">|   B,C   || D |
+| b,c,d,e || ∅ |
 </t>
         </is>
       </c>
@@ -999,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>1.817247</v>
+        <v>1.89279</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1013,8 +1013,8 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">|   B   || C,D |
-| b,c,d ||  ∅  |
+          <t xml:space="preserve">|  B,C  || D |
+| b,c,d || ∅ |
 </t>
         </is>
       </c>
@@ -1022,7 +1022,7 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>1.780941</v>
+        <v>1.877934</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1036,8 +1036,8 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">|  B  || C,D |
-| c,e ||  a  |
+          <t xml:space="preserve">| B,C,D || ∅ |
+|  c,e  || a |
 </t>
         </is>
       </c>
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>1.803232</v>
+        <v>1.79012</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1059,8 +1059,8 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">| B,C,D ||  ∅  |
-|   ∅   || b,d |
+          <t xml:space="preserve">| B,C || D |
+| b,d || ∅ |
 </t>
         </is>
       </c>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>1.81902</v>
+        <v>1.872139</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1082,8 +1082,8 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">|  B  || C,D |
-| d,e || a,b |
+          <t xml:space="preserve">| B ||   C,D   |
+| ∅ || a,b,d,e |
 </t>
         </is>
       </c>
@@ -1091,7 +1091,7 @@
         <v>0.25</v>
       </c>
       <c r="D29" t="n">
-        <v>1.899682</v>
+        <v>1.829288</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>0.5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.882268</v>
+        <v>1.850625</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>0.75</v>
       </c>
       <c r="D31" t="n">
-        <v>1.823702</v>
+        <v>1.849435</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1.795692</v>
+        <v>1.791165</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1.807761</v>
+        <v>1.812199</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1197,8 +1197,8 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">|  A  || C,E |
-| c,e ||  a  |
+          <t xml:space="preserve">| A,C,E || ∅ |
+|  c,e  || a |
 </t>
         </is>
       </c>
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1.807019</v>
+        <v>1.867427</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>1.747832</v>
+        <v>1.802938</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1243,16 +1243,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,C,E ||  ∅  |
-|  a,b  || d,e |
+          <t xml:space="preserve">|  A,C,E  || ∅ |
+| a,b,d,e || ∅ |
 </t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>1.837208</v>
+        <v>1.808223</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">|    B    || D |
+          <t xml:space="preserve">|   B,D   || ∅ |
 | b,c,d,e || a |
 </t>
         </is>
@@ -1275,7 +1275,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>1.873564</v>
+        <v>1.828396</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">|   B   || D |
+          <t xml:space="preserve">|  B,D  || ∅ |
 | b,c,d || a |
 </t>
         </is>
@@ -1298,7 +1298,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>1.814766</v>
+        <v>1.774041</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>1.8615</v>
+        <v>1.796522</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>1.770298</v>
+        <v>1.809319</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">|  B  || D |
+          <t xml:space="preserve">| B,D || ∅ |
 | c,e || a |
 </t>
         </is>
@@ -1367,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1.741262</v>
+        <v>1.79942</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1381,8 +1381,8 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">| B,D ||  ∅  |
-|  ∅  || b,d |
+          <t xml:space="preserve">|  B  || D |
+| b,d || ∅ |
 </t>
         </is>
       </c>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1.806262</v>
+        <v>1.747026</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">|   B   || D |
+          <t xml:space="preserve">|  B,D  || ∅ |
 | b,d,e || a |
 </t>
         </is>
@@ -1413,7 +1413,7 @@
         <v>0.25</v>
       </c>
       <c r="D43" t="n">
-        <v>1.881742</v>
+        <v>1.817246</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">|  A,B,E  || D |
+          <t xml:space="preserve">| A,B,D,E || ∅ |
 | b,c,d,e || a |
 </t>
         </is>
@@ -1436,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>1.941208</v>
+        <v>1.775659</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1450,8 +1450,8 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,B,D,E || ∅ |
-|  a,b,c  || d |
+          <t xml:space="preserve">| A,B,E || D |
+| a,b,c || d |
 </t>
         </is>
       </c>
@@ -1459,7 +1459,7 @@
         <v>0.5</v>
       </c>
       <c r="D45" t="n">
-        <v>1.835059</v>
+        <v>1.837346</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>1.925918</v>
+        <v>1.781111</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>1.789876</v>
+        <v>1.82513</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1519,8 +1519,8 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,B || D,E |
-| c,e ||  a  |
+          <t xml:space="preserve">| A,B,D,E || ∅ |
+|   c,e   || a |
 </t>
         </is>
       </c>
@@ -1528,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>1.839561</v>
+        <v>1.787569</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1542,8 +1542,8 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,E || B,D |
-| b,d ||  ∅  |
+          <t xml:space="preserve">| A,B,E || D |
+|  b,d  || ∅ |
 </t>
         </is>
       </c>
@@ -1551,7 +1551,7 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>1.809924</v>
+        <v>1.813842</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1565,8 +1565,8 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,B,E || D |
-| b,d,e || a |
+          <t xml:space="preserve">| A,B,D,E || ∅ |
+|  b,d,e  || a |
 </t>
         </is>
       </c>
@@ -1574,7 +1574,7 @@
         <v>0.25</v>
       </c>
       <c r="D50" t="n">
-        <v>1.875835</v>
+        <v>1.764056</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1586,14 +1586,18 @@
       <c r="A51" t="n">
         <v>50</v>
       </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|   B   || E |
+| c,d,e || b |
+</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>1.771915</v>
+        <v>1.83396</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>

--- a/5A_Geometric.xlsx
+++ b/5A_Geometric.xlsx
@@ -461,16 +461,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,B,C,D,E || ∅ |
-|  b,c,d,e  || a |
+          <t xml:space="preserve">|  A,B,C,E  || D |
+| a,b,c,d,e || ∅ |
 </t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.873759</v>
+        <v>1.81561</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -484,16 +484,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,C,E || B,D |
-|  a,b  || c,d |
+          <t xml:space="preserve">| A,B,C,E || D |
+| a,b,c,d || ∅ |
 </t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.823528</v>
+        <v>1.802442</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1.774792</v>
+        <v>1.688257</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1.78864</v>
+        <v>2.017864</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1.83843</v>
+        <v>1.807464</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1.799211</v>
+        <v>1.715113</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -599,16 +599,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,C,D,E || B |
+          <t xml:space="preserve">| A,B,C,E || D |
 | a,b,d,e || ∅ |
 </t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1.806211</v>
+        <v>1.766191</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -622,16 +622,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,B,C,D || ∅ |
-| b,c,d,e || a |
+          <t xml:space="preserve">|   A,B,C   || D |
+| a,b,c,d,e || ∅ |
 </t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1.89056</v>
+        <v>1.789427</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -645,16 +645,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,C || B,D |
-| a,b || c,d |
+          <t xml:space="preserve">|  A,B,C  || D |
+| a,b,c,d || ∅ |
 </t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1.809347</v>
+        <v>1.700775</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1.838888</v>
+        <v>1.754629</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1.880995</v>
+        <v>1.758276</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1.79999</v>
+        <v>1.746087</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1.872529</v>
+        <v>1.699157</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -760,16 +760,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">|  A,C,D  || B |
+          <t xml:space="preserve">|  A,B,C  || D |
 | a,b,d,e || ∅ |
 </t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1.775582</v>
+        <v>1.803549</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -783,8 +783,8 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">|  B,D  || C,E |
-| c,d,e || a,b |
+          <t xml:space="preserve">| B,D ||   C,E   |
+|  c  || a,b,d,e |
 </t>
         </is>
       </c>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1.852542</v>
+        <v>1.811394</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">| B,C,D,E || ∅ |
+          <t xml:space="preserve">|  B,C,E  || D |
 | a,b,c,d || ∅ |
 </t>
         </is>
@@ -815,7 +815,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1.860578</v>
+        <v>1.720499</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.785794</v>
+        <v>1.759023</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1.768596</v>
+        <v>1.759282</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1.850605</v>
+        <v>1.710705</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1.741389</v>
+        <v>1.762948</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -921,16 +921,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">| B ||  C,D,E  |
-| ∅ || a,b,d,e |
+          <t xml:space="preserve">|  B,C,E  || D |
+| a,b,d,e || ∅ |
 </t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1.844047</v>
+        <v>1.77249</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -944,8 +944,8 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">|  B,D  ||  C  |
-| c,d,e || a,b |
+          <t xml:space="preserve">| B,D ||    C    |
+|  c  || a,b,d,e |
 </t>
         </is>
       </c>
@@ -953,7 +953,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1.835869</v>
+        <v>1.827672</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">|  B,C,D  || ∅ |
+          <t xml:space="preserve">|   B,C   || D |
 | a,b,c,d || ∅ |
 </t>
         </is>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1.764995</v>
+        <v>1.74876</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>1.89279</v>
+        <v>1.789359</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>1.877934</v>
+        <v>1.781637</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>1.79012</v>
+        <v>1.760952</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>1.872139</v>
+        <v>1.722528</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">| B ||   C,D   |
-| ∅ || a,b,d,e |
+          <t xml:space="preserve">|   B,C   || D |
+| a,b,d,e || ∅ |
 </t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>1.829288</v>
+        <v>1.730209</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>0.5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.850625</v>
+        <v>1.82029</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1128,16 +1128,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,C,E ||  ∅  |
-|  a,b  || c,d |
+          <t xml:space="preserve">| A ||   C,E   |
+| ∅ || a,b,c,d |
 </t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="D31" t="n">
-        <v>1.849435</v>
+        <v>1.820161</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1.791165</v>
+        <v>1.775401</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1.812199</v>
+        <v>1.748025</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1.867427</v>
+        <v>1.798038</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>1.802938</v>
+        <v>1.739899</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1243,16 +1243,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">|  A,C,E  || ∅ |
-| a,b,d,e || ∅ |
+          <t xml:space="preserve">| A,C,E || ∅ |
+| b,d,e || a |
 </t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D36" t="n">
-        <v>1.808223</v>
+        <v>1.710855</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>1.828396</v>
+        <v>1.736795</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>1.774041</v>
+        <v>1.708971</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>1.796522</v>
+        <v>1.681031</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>1.809319</v>
+        <v>1.700399</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1.79942</v>
+        <v>1.768587</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1.747026</v>
+        <v>1.780741</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1404,16 +1404,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">|  B,D  || ∅ |
-| b,d,e || a |
+          <t xml:space="preserve">|  B  ||  D  |
+| a,e || b,d |
 </t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>1.817246</v>
+        <v>1.773794</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>1.775659</v>
+        <v>1.845402</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1450,16 +1450,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,B,E || D |
-| a,b,c || d |
+          <t xml:space="preserve">|  A,B,E  || D |
+| a,b,c,d || ∅ |
 </t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>1.837346</v>
+        <v>1.768229</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>1.781111</v>
+        <v>1.694933</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>1.82513</v>
+        <v>1.770749</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>1.787569</v>
+        <v>1.716317</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>1.813842</v>
+        <v>1.746995</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1565,16 +1565,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">| A,B,D,E || ∅ |
-|  b,d,e  || a |
+          <t xml:space="preserve">| A,D,E ||  B  |
+|  b,d  || a,e |
 </t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>1.764056</v>
+        <v>1.750733</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1588,8 +1588,8 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">|   B   || E |
-| c,d,e || b |
+          <t xml:space="preserve">|  B  ||  E  |
+| c,d || b,e |
 </t>
         </is>
       </c>
@@ -1597,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>1.83396</v>
+        <v>1.705362</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
